--- a/output/roomself_excel/8612.xlsx
+++ b/output/roomself_excel/8612.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>513999</v>
+        <v>103395</v>
       </c>
       <c r="D2" t="n">
-        <v>9024</v>
+        <v>2752</v>
       </c>
       <c r="E2" t="n">
-        <v>1084</v>
+        <v>483</v>
       </c>
       <c r="F2" t="n">
-        <v>630</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>119340</v>
+        <v>236876</v>
       </c>
       <c r="D3" t="n">
-        <v>2876</v>
+        <v>3960</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>630</v>
       </c>
       <c r="F3" t="n">
-        <v>282</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>135538</v>
+        <v>173728</v>
       </c>
       <c r="D4" t="n">
-        <v>3072</v>
+        <v>5036</v>
       </c>
       <c r="E4" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="F4" t="n">
-        <v>331</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28210</v>
+        <v>16492</v>
       </c>
       <c r="D5" t="n">
-        <v>1388</v>
+        <v>1028</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>379</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37310</v>
+        <v>25707</v>
       </c>
       <c r="D6" t="n">
-        <v>1548</v>
+        <v>1328</v>
       </c>
       <c r="E6" t="n">
-        <v>625</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>182</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75200</v>
+        <v>54516</v>
       </c>
       <c r="D7" t="n">
-        <v>3204</v>
+        <v>1868</v>
       </c>
       <c r="E7" t="n">
-        <v>625</v>
+        <v>259</v>
       </c>
       <c r="F7" t="n">
-        <v>593</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2944</v>
+        <v>119340</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>2876</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18860</v>
+        <v>135538</v>
       </c>
       <c r="D9" t="n">
-        <v>1188</v>
+        <v>3072</v>
       </c>
       <c r="E9" t="n">
-        <v>625</v>
+        <v>480</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88140</v>
+        <v>28210</v>
       </c>
       <c r="D10" t="n">
-        <v>2396</v>
+        <v>1388</v>
       </c>
       <c r="E10" t="n">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="F10" t="n">
-        <v>282</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>93197</v>
+        <v>37310</v>
       </c>
       <c r="D11" t="n">
-        <v>2592</v>
+        <v>1548</v>
       </c>
       <c r="E11" t="n">
-        <v>331</v>
+        <v>182</v>
       </c>
       <c r="F11" t="n">
-        <v>320</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25707</v>
+        <v>75200</v>
       </c>
       <c r="D12" t="n">
-        <v>1328</v>
+        <v>3204</v>
       </c>
       <c r="E12" t="n">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16492</v>
+        <v>2944</v>
       </c>
       <c r="D13" t="n">
-        <v>1028</v>
+        <v>440</v>
       </c>
       <c r="E13" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>54516</v>
+        <v>18860</v>
       </c>
       <c r="D14" t="n">
-        <v>1868</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
-        <v>259</v>
+        <v>437</v>
       </c>
       <c r="F14" t="n">
-        <v>236</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>88140</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E15" t="n">
+        <v>370</v>
+      </c>
+      <c r="F15" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2592</v>
+      </c>
+      <c r="E16" t="n">
+        <v>331</v>
+      </c>
+      <c r="F16" t="n">
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8612.xlsx
+++ b/output/roomself_excel/8612.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2752</v>
       </c>
-      <c r="E2" t="n">
-        <v>483</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>251</v>
+        <v>460</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>217</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3960</v>
       </c>
-      <c r="E3" t="n">
-        <v>630</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>426</v>
+        <v>584</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>811</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>5036</v>
       </c>
-      <c r="E4" t="n">
-        <v>630</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>500</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>1028</v>
       </c>
-      <c r="E5" t="n">
-        <v>379</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>147</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,20 @@
       <c r="D6" t="n">
         <v>1328</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>123</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>23</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>1868</v>
       </c>
-      <c r="E7" t="n">
-        <v>259</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>236</v>
+        <v>472</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>231</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>2876</v>
       </c>
-      <c r="E8" t="n">
-        <v>481</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>282</v>
+        <v>248</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>459</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +737,27 @@
       <c r="D9" t="n">
         <v>3072</v>
       </c>
-      <c r="E9" t="n">
-        <v>480</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>331</v>
+        <v>297</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>430</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +775,20 @@
       <c r="D10" t="n">
         <v>1388</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>130</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>23</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +805,20 @@
       <c r="D11" t="n">
         <v>1548</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>182</v>
       </c>
-      <c r="F11" t="n">
-        <v>22</v>
-      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +835,20 @@
       <c r="D12" t="n">
         <v>3204</v>
       </c>
-      <c r="E12" t="n">
-        <v>625</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
         <v>222</v>
       </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +865,12 @@
       <c r="D13" t="n">
         <v>440</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +887,20 @@
       <c r="D14" t="n">
         <v>1188</v>
       </c>
-      <c r="E14" t="n">
-        <v>437</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
         <v>92</v>
       </c>
+      <c r="G14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +917,27 @@
       <c r="D15" t="n">
         <v>2396</v>
       </c>
-      <c r="E15" t="n">
-        <v>370</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>282</v>
+        <v>339</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>260</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -783,11 +955,27 @@
       <c r="D16" t="n">
         <v>2592</v>
       </c>
-      <c r="E16" t="n">
-        <v>331</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>320</v>
+        <v>286</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>309</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
